--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486749_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486749_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8744</v>
+        <v>5.6824</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3831</v>
+        <v>7.0105</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5087</v>
+        <v>-1.3281</v>
       </c>
       <c r="G2" t="n">
         <v>4.6789</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.3932</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1314</v>
+        <v>-0.5039</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7166</v>
+        <v>0.8972</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5482</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5069</v>
+        <v>0.3446</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6056</v>
+        <v>0.1377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9176</v>
+        <v>0.1309</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.312</v>
+        <v>0.0068</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7236</v>
+        <v>0.0621</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3317</v>
+        <v>0.0621</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6081</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1181</v>
+        <v>0.0756</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4142</v>
+        <v>0.0689</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2961</v>
+        <v>0.0068</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1291</v>
+        <v>0.0138</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0957</v>
+        <v>0.0275</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0333</v>
+        <v>-0.0137</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2701</v>
+        <v>0.306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0896</v>
+        <v>2.6763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1805</v>
+        <v>-2.3703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1377</v>
+        <v>1.9269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1309</v>
+        <v>1.6489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0068</v>
+        <v>0.278</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0621</v>
+        <v>6.1975</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0621</v>
+        <v>3.5118</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.6857</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0756</v>
+        <v>-4.2706</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0689</v>
+        <v>-1.8629</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0068</v>
+        <v>-2.4077</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1931</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0607</v>
+        <v>-0.0414</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0275</v>
+        <v>0.0547</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0882</v>
+        <v>-0.0961</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3513</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1211</v>
+        <v>0.0053</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5659</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4448</v>
+        <v>0.668</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9269</v>
+        <v>0.6056</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6489</v>
+        <v>0.9176</v>
       </c>
       <c r="I5" t="n">
-        <v>0.278</v>
+        <v>-0.312</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1975</v>
+        <v>0.7236</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5118</v>
+        <v>1.3317</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6857</v>
+        <v>-0.6081</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.2706</v>
+        <v>-0.1181</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8629</v>
+        <v>-0.4142</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4077</v>
+        <v>0.2961</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.9308</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-3.8616</v>
       </c>
       <c r="R5" t="n">
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2262</v>
+        <v>0.6274</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0557</v>
+        <v>0.5444</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1706</v>
+        <v>0.083</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3513</v>
+        <v>-1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3476</v>
+        <v>-0.2782</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.924</v>
+        <v>-1.2018</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5764</v>
+        <v>0.9236</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5794</v>
+        <v>0.5149</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3036</v>
+        <v>0.5239</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2758</v>
+        <v>-0.0091</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6481</v>
+        <v>-0.1122</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0414</v>
+        <v>0.4552</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6895</v>
+        <v>-0.5674</v>
       </c>
       <c r="M6" t="n">
+        <v>0.6271</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.0687</v>
       </c>
-      <c r="N6" t="n">
-        <v>-0.345</v>
-      </c>
       <c r="O6" t="n">
-        <v>0.4137</v>
+        <v>0.5583</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0387</v>
+        <v>0.0138</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2759</v>
+        <v>-0.1242</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3146</v>
+        <v>0.1381</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.4517</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4087</v>
+        <v>2.4152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6753</v>
+        <v>-2.8669</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5149</v>
+        <v>-1.5131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5239</v>
+        <v>-1.3729</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0091</v>
+        <v>-0.1402</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1122</v>
+        <v>1.6608</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4552</v>
+        <v>-0.3377</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5674</v>
+        <v>1.9985</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6271</v>
+        <v>-3.1739</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0687</v>
+        <v>-1.0352</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5583</v>
+        <v>-2.1387</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4413</v>
+        <v>-0.0276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>0.2065</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1102</v>
+        <v>-0.234</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6138</v>
+        <v>-0.2626</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6138</v>
+        <v>-1.7759</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALDERREY PULIDO</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0147</v>
+        <v>-0.4966</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2973</v>
+        <v>-0.924</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7174</v>
+        <v>0.4274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1302</v>
+        <v>-0.5794</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7858000000000001</v>
+        <v>-0.3036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.2758</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6348</v>
+        <v>-0.6481</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8209</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8138</v>
+        <v>-0.6895</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5046</v>
+        <v>0.0687</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0351</v>
+        <v>-0.345</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4695</v>
+        <v>0.4137</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4302</v>
+        <v>-0.1103</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6071</v>
+        <v>-0.2759</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1769</v>
+        <v>0.1656</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6369</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>J. VALDERREY PULIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3602</v>
+        <v>-0.7775</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2345</v>
+        <v>-0.0353</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1257</v>
+        <v>-0.7423</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1174</v>
+        <v>0.1302</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4415</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0414</v>
+        <v>2.6348</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>1.8209</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.8138</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1588</v>
+        <v>-2.5046</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4829</v>
+        <v>-1.0351</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.4695</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2428</v>
+        <v>-0.193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>-0.3451</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0331</v>
+        <v>0.152</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6369</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5054</v>
+        <v>-1.3106</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6843</v>
+        <v>-0.2345</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1897</v>
+        <v>-1.076</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5131</v>
+        <v>-1.1174</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3729</v>
+        <v>-0.4415</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1402</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6608</v>
+        <v>0.0414</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3377</v>
+        <v>0.0414</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9985</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1739</v>
+        <v>-1.1588</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0352</v>
+        <v>-0.4829</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1387</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3169</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0813</v>
+        <v>-0.1931</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5244</v>
+        <v>-0.2759</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5569</v>
+        <v>0.0828</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2626</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0088</v>
+        <v>-3.4681</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4408</v>
+        <v>-4.1236</v>
       </c>
       <c r="F11" t="n">
-        <v>0.432</v>
+        <v>0.6555</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5142</v>
@@ -1312,13 +1312,13 @@
         <v>2.8962</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5683</v>
+        <v>-0.0276</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3591</v>
+        <v>-0.0419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2092</v>
+        <v>0.0143</v>
       </c>
       <c r="V11" t="n">
         <v>0.1083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3967</v>
+        <v>-4.5981</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9627</v>
+        <v>-2.1144</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.434</v>
+        <v>-2.4837</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5804</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>0.022</v>
+        <v>-0.1794</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0548</v>
+        <v>-0.0968</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0329</v>
+        <v>-0.0825</v>
       </c>
       <c r="V12" t="n">
         <v>1.5133</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5943</v>
+        <v>-5.042499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3435</v>
+        <v>2.895199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.9377</v>
+        <v>-7.9378</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3103</v>
@@ -1468,28 +1468,28 @@
         <v>16.4116</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2758</v>
+        <v>0.2757999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3826</v>
+        <v>-0.8306</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1065</v>
+        <v>1.1067</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.04249999999999976</v>
+        <v>-0.04249999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>4.1264</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.169100000000001</v>
+        <v>-4.1691</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2805</v>
+        <v>5.527</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6008</v>
+        <v>4.948</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6797</v>
+        <v>0.579</v>
       </c>
       <c r="G14" t="n">
-        <v>0.063</v>
+        <v>2.8709</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3932</v>
+        <v>0.7029</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3301</v>
+        <v>2.168</v>
       </c>
       <c r="J14" t="n">
-        <v>3.12</v>
+        <v>6.4104</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6701</v>
+        <v>3.1866</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4499</v>
+        <v>3.2238</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0569</v>
+        <v>-3.5395</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2769</v>
+        <v>-2.4837</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.78</v>
+        <v>-1.0558</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2823</v>
+        <v>1.5446</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2823</v>
+        <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6495</v>
+        <v>0.455</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9096</v>
+        <v>-0.497</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7399</v>
+        <v>0.952</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2856</v>
+        <v>0.6565</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6922</v>
+        <v>4.6723</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7256</v>
+        <v>3.8769</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9665</v>
+        <v>0.7954</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6219</v>
+        <v>0.063</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3584</v>
+        <v>0.3932</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9803</v>
+        <v>-0.3301</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2239</v>
+        <v>3.12</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3325</v>
+        <v>2.6701</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8914</v>
+        <v>0.4499</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6021</v>
+        <v>-3.0569</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6909</v>
+        <v>-2.2769</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9111</v>
+        <v>-0.78</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>3.2823</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4754</v>
+        <v>3.2823</v>
       </c>
       <c r="S15" t="n">
-        <v>2.306</v>
+        <v>1.0413</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2128</v>
+        <v>0.1857</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0932</v>
+        <v>0.8556</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1851</v>
+        <v>0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1851</v>
+        <v>0.5712</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1122</v>
+        <v>3.4757</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1207</v>
+        <v>2.6914</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.7843</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8709</v>
+        <v>0.6219</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7029</v>
+        <v>-1.3584</v>
       </c>
       <c r="I16" t="n">
-        <v>2.168</v>
+        <v>1.9803</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4104</v>
+        <v>4.2239</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1866</v>
+        <v>1.3325</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2238</v>
+        <v>2.8914</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5395</v>
+        <v>-3.6021</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4837</v>
+        <v>-2.6909</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0558</v>
+        <v>-0.9111</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R16" t="n">
-        <v>2.51</v>
+        <v>3.4754</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9599</v>
+        <v>1.0895</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3244</v>
+        <v>0.1786</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3645</v>
+        <v>0.9109</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6565</v>
+        <v>1.1851</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2327</v>
+        <v>1.1349</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8583</v>
+        <v>0.548</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3745</v>
+        <v>0.5868</v>
       </c>
       <c r="G17" t="n">
         <v>0.4963</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6012</v>
+        <v>0.5034</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3584</v>
+        <v>0.0481</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2429</v>
+        <v>0.4553</v>
       </c>
       <c r="V17" t="n">
         <v>0.3282</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2776</v>
+        <v>0.1093</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5309</v>
+        <v>1.3277</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7467</v>
+        <v>-1.2185</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4692</v>
+        <v>0.0201</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6138</v>
+        <v>-0.6492</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1447</v>
+        <v>0.6693</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3376</v>
+        <v>3.008</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3376</v>
+        <v>1.2829</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.7251</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1316</v>
+        <v>-2.9879</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2763</v>
+        <v>-1.9321</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1447</v>
+        <v>-1.0558</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>2.3169</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>3.2823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6123</v>
+        <v>-0.3862</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1928</v>
+        <v>-0.3866</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4195</v>
+        <v>0.0004</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6138</v>
+        <v>-1.8415</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6138</v>
+        <v>-0.3282</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4794</v>
+        <v>-1.7865</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5004</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9798</v>
+        <v>-0.9454</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0201</v>
+        <v>-1.4692</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6492</v>
+        <v>-1.6138</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6693</v>
+        <v>0.1447</v>
       </c>
       <c r="J19" t="n">
-        <v>3.008</v>
+        <v>-1.3376</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2829</v>
+        <v>-1.3376</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7251</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9879</v>
+        <v>-0.1316</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9321</v>
+        <v>-0.2763</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0558</v>
+        <v>0.1447</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3169</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2823</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9749</v>
+        <v>0.1034</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.214</v>
+        <v>-0.1174</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7609</v>
+        <v>0.2208</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8415</v>
+        <v>-0.6138</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3282</v>
+        <v>0.6138</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5891</v>
+        <v>-2.618</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.904</v>
+        <v>-3.0074</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3149</v>
+        <v>0.3894</v>
       </c>
       <c r="G20" t="n">
         <v>1.722</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0055</v>
+        <v>-0.0344</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0135</v>
       </c>
       <c r="V20" t="n">
         <v>0.3282</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.377</v>
+        <v>-2.8517</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.433</v>
+        <v>-1.6057</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9439</v>
+        <v>-1.246</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0146</v>
@@ -2092,13 +2092,13 @@
         <v>2.7031</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9529</v>
+        <v>-0.4276</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3244</v>
+        <v>-0.497</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.594499999999998</v>
+        <v>7.663000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>7.937899999999999</v>
+        <v>7.9377</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3433</v>
+        <v>-0.2750000000000004</v>
       </c>
       <c r="G22" t="n">
         <v>4.3104</v>
@@ -2170,13 +2170,13 @@
         <v>17.377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2757999999999998</v>
+        <v>2.3444</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1067</v>
+        <v>-1.1065</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3826</v>
+        <v>3.4509</v>
       </c>
       <c r="V22" t="n">
         <v>0.04269999999999996</v>
